--- a/AItalimat.xlsx
+++ b/AItalimat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erenholding-my.sharepoint.com/personal/ernkit03_erenenerji_com_tr/Documents/Masaüstü/FocusPro-yeni/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_AD4D0BC4A776854ACB15BCE3FE90EC98693EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96597CBE-8C05-408B-98D4-63DDBD634C75}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_AD4D0BC4A776854ACB15BCE3FE90EC98693EDF1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4DE5E8B1-EBF8-424E-B845-B291FA55F58B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,61 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
-  <si>
-    <t>Çocuk testinde hızlanma ve yavaşlama</t>
-  </si>
-  <si>
-    <t>* 0–2 dk: yavaş ve öğretici tempo →  Ana simge Hızı 1800 ms  ( Sesli ve sessiz Gif yok , Sadece Ses yok )</t>
-  </si>
-  <si>
-    <t>* 2–5 dk: temel tempo → 1700 ms   ( Sesli ve sessiz Gif yok , Sadece Ses yok )</t>
-  </si>
-  <si>
-    <t>* 5–7 dk: hafif hızlanma → 1600 ms  ( Sesli ve sessiz Gif yok , Sadece Ses yok )</t>
-  </si>
-  <si>
-    <t>* 7–10 dk: görsel çeldirici + aynı tempo → 1600 ms ( Sadece sessiz gifler olacak aynı anda sadece 2 gif olacak Gifler en fazla 10 sn ekranda kalacak. Giflerin ekrana geliş süresi ana simgeden bağımsız olacak. 3 dk boyunca  sessiz gifler sürekli ekrana gelecek ekranda hiç gif olmama süresi maks. 2 sn olacak.)</t>
-  </si>
-  <si>
-    <t>* 10–11 dk: işitsel çeldirici + aynı tempo → 1500 ms (</t>
-  </si>
-  <si>
-    <t>* 11-12 dk: görsel işitsel çeldirici + aynı tempo → 1500 ms</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>12–13 dk: toparlanma / yavaşlama → 1850 ms</t>
-  </si>
-  <si>
-    <t>Ergen testinde hızlanma ve yavaşlama</t>
-  </si>
-  <si>
-    <t>* 0–2 dk: alışma temposu → 1400 ms</t>
-  </si>
-  <si>
-    <t>* 2–5 dk: temel tempo → 1200 ms</t>
-  </si>
-  <si>
-    <t>* 5–7 dk: hızlanma → 1000 ms</t>
-  </si>
-  <si>
-    <t>* 7–9 dk: görsel çeldirici + orta tempo → 1100 ms</t>
-  </si>
-  <si>
-    <t>* 9-10 dk: işitsel çeldirici + orta tempo → 1000 ms</t>
-  </si>
-  <si>
-    <t>* 10–13 dk:     görsel + işitsel birlikte yorgunluk + hız baskısı → 900 ms</t>
-  </si>
-  <si>
-    <t>* 13–14 dk: çeldirici yok toparlanma / yavaşlama → 1300 ms</t>
-  </si>
-  <si>
-    <t>Süre: 14 dakika</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="53">
   <si>
     <t>Yetişkin</t>
   </si>
@@ -155,6 +101,94 @@
   <si>
     <t>Evet 
 Sadece sessiz gifler olacak aynı anda sadece 2 gif olacak Gifler en fazla 10 sn ekranda kalacak. Giflerin ekrana geliş süresi ana simgeden bağımsız olacak. 3 dk boyunca  sessiz gifler sürekli ekrana gelecek ekranda hiç gif olmama süresi maks. 2 sn olacak.</t>
+  </si>
+  <si>
+    <t>10- 11 dk</t>
+  </si>
+  <si>
+    <t>Evet 
+Sadece seslerr olacak aynı anda sadece 1  ses olacak sesler en fazla 10 sn duyulacak. Seslerin ekrana geliş süresi ana simgeden bağımsız olacak. 1 dk boyunca  seslerr sürekli gelecek ekranda hiç ses olmama süresi maks. 2 sn olacak. 1 dk tamamlanıncada sesler duracak</t>
+  </si>
+  <si>
+    <t>11-12 dk</t>
+  </si>
+  <si>
+    <t>12–13 dk</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1850 ms</t>
+  </si>
+  <si>
+    <t>yok</t>
+  </si>
+  <si>
+    <t>Bu 1 dakikalık süreçte sesli ve sessiz gifler ekrana aynı anda gelecek. Ekrana aynı anda maksimum 1 adet sesli gif gelecek. Sesli ve sessiz gifin ekrana geliş süresi birbirinden ayrı olacak. 
+Sesli ve sessizgiflerin ekrana geliş süresi ana simgeden bağımsız olacak. 1 dk boyunca  gifler sürekli gelecek ekranda hiç gif olmama süresi maks. 2 sn olacak. 1 dk tamamlanıncada gifler duracak</t>
+  </si>
+  <si>
+    <t>Test Grubu : Ergen</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1400 ms</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1200 ms</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1000 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 7–9 dk</t>
+  </si>
+  <si>
+    <t>9- 10 dk</t>
+  </si>
+  <si>
+    <t>10-13 dk</t>
+  </si>
+  <si>
+    <t>13–14 dk</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1300 ms</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1100 ms</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 900 ms</t>
+  </si>
+  <si>
+    <t>Evet 
+Sadece sessiz gifler olacak aynı anda sadece 2 gif olacak Gifler en fazla 10 sn ekranda kalacak. Giflerin ekrana geliş süresi ana simgeden bağımsız olacak. 2 dk boyunca  sessiz gifler sürekli ekrana gelecek ekranda hiç gif olmama süresi maks. 2 sn olacak.</t>
+  </si>
+  <si>
+    <t>Bu 3 dakikalık süreçte sesli ve sessiz gifler ekrana aynı anda gelecek. Ekrana aynı anda maksimum 1 adet sesli gif gelecek. Sesli ve sessiz gifin ekrana geliş süresi birbirinden ayrı olacak. 
+Sesli ve sessizgiflerin ekrana geliş süresi ana simgeden bağımsız olacak. 3 dk boyunca  gifler sürekli gelecek ekranda hiç gif olmama süresi maks. 2 sn olacak. 3 dk tamamlanıncada gifler duracak</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0–3 dk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3–6 dk</t>
+  </si>
+  <si>
+    <t>Ana simge Hızı 1000 ms ile başlayıp her dakika 100 ms azalacak 9. dk 800 ms ile tamamlanacaktır</t>
+  </si>
+  <si>
+    <t>6–9 dk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 9–11 dk</t>
+  </si>
+  <si>
+    <t>12- 14 dk</t>
+  </si>
+  <si>
+    <t>14-15 dk</t>
+  </si>
+  <si>
+    <t>115–14 dk</t>
   </si>
 </sst>
 </file>
@@ -184,7 +218,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -192,20 +226,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,297 +542,547 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E58"/>
+  <dimension ref="A2:U48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.140625" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="5" width="21" customWidth="1"/>
+    <col min="3" max="6" width="29.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="N2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+    </row>
+    <row r="3" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="U3" s="1"/>
+    </row>
+    <row r="4" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U4" s="1"/>
+    </row>
+    <row r="5" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U5" s="1"/>
+    </row>
+    <row r="6" spans="1:21" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U6" s="1"/>
+    </row>
+    <row r="7" spans="1:21" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="P7" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U7" s="1"/>
+    </row>
+    <row r="8" spans="1:21" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="U8" s="1"/>
+    </row>
+    <row r="9" spans="1:21" ht="159.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="H9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="U9" s="1"/>
+    </row>
+    <row r="10" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B10" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
+      <c r="H10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="155.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="I10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="P10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G13" s="1"/>
+    </row>
+    <row r="14" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:21" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G22" s="1"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="6">
     <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P9:Q9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -789,6 +1094,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{6beccce0-6c7b-48b8-93f3-a6e4d786204b}" enabled="1" method="Privileged" siteId="{bcb5eab3-872d-4e34-9dc5-8ac3d404c0c9}" removed="0"/>
+  <clbl:label id="{6beccce0-6c7b-48b8-93f3-a6e4d786204b}" enabled="1" method="Privileged" SiteId="bcb5eab3-872d-4e34-9dc5-8ac3d404c0c9" removed="0"/>
 </clbl:labelList>
 </file>